--- a/data/vendor-search/results_all_airpurifier.xlsx
+++ b/data/vendor-search/results_all_airpurifier.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,6 +450,11 @@
       <c r="G1" t="inlineStr">
         <is>
           <t>cpe_strings</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
         </is>
       </c>
     </row>
